--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:01</t>
+    <t xml:space="preserve">2026-09-10 01:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:13</t>
+    <t xml:space="preserve">2026-09-12 22:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:25</t>
+    <t xml:space="preserve">2026-09-23 23:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:54</t>
+    <t xml:space="preserve">2026-10-02 15:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -114,10 +114,10 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Álamos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Hualpén</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:50</t>
+    <t xml:space="preserve">2026-10-04 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2024_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:35</t>
+    <t xml:space="preserve">2026-10-05 16:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
